--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_3.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_3.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20640" windowHeight="8820"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表2-3除回购和拆借外贷款分地区" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,7 @@
     <definedName name="Err">[1]综合校验!$B$2</definedName>
     <definedName name="Thd">[1]综合校验!$B$1</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -31,6 +36,7 @@
         <b/>
         <sz val="16"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 除回购和拆借外贷款分地区统计模板</t>
@@ -56,9 +62,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>单位：万元</t>
-  </si>
-  <si>
     <t>列编号</t>
   </si>
   <si>
@@ -90,6 +93,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>01</t>
@@ -98,6 +102,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -117,6 +122,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>02</t>
@@ -125,6 +131,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -144,6 +151,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>03</t>
@@ -152,6 +160,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -171,6 +180,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>04</t>
@@ -179,6 +189,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -198,6 +209,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>05</t>
@@ -206,6 +218,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -225,6 +238,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>06</t>
@@ -233,6 +247,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -252,6 +267,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>06</t>
@@ -260,6 +276,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>001</t>
@@ -279,6 +296,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>07</t>
@@ -287,6 +305,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -306,6 +325,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>08</t>
@@ -314,6 +334,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -333,6 +354,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>09</t>
@@ -341,6 +363,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -360,6 +383,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>10</t>
@@ -368,6 +392,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -387,6 +412,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>11</t>
@@ -395,6 +421,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -414,6 +441,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>11</t>
@@ -422,6 +450,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>001</t>
@@ -441,6 +470,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>12</t>
@@ -449,6 +479,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -468,6 +499,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>13</t>
@@ -476,6 +508,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -495,6 +528,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>13</t>
@@ -503,6 +537,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>001</t>
@@ -522,6 +557,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>14</t>
@@ -530,6 +566,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -549,6 +586,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>15</t>
@@ -557,6 +595,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -576,6 +615,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>15</t>
@@ -584,6 +624,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>001</t>
@@ -603,6 +644,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>16</t>
@@ -611,6 +653,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -630,6 +673,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>17</t>
@@ -638,6 +682,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -657,6 +702,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>18</t>
@@ -665,6 +711,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -684,6 +731,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>19</t>
@@ -692,6 +740,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -711,6 +760,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>19</t>
@@ -719,6 +769,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>001</t>
@@ -738,6 +789,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>20</t>
@@ -746,6 +798,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -765,6 +818,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>21</t>
@@ -773,6 +827,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -792,6 +847,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>22</t>
@@ -800,6 +856,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -819,6 +876,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>23</t>
@@ -827,6 +885,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -846,6 +905,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>24</t>
@@ -854,6 +914,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -873,6 +934,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>25</t>
@@ -881,6 +943,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -900,6 +963,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>26</t>
@@ -908,6 +972,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -927,6 +992,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>27</t>
@@ -935,6 +1001,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -954,6 +1021,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>28</t>
@@ -962,6 +1030,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -981,6 +1050,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>29</t>
@@ -989,6 +1059,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -1008,6 +1079,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>30</t>
@@ -1016,6 +1088,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -1029,6 +1102,8 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>宁夏</t>
     </r>
@@ -1044,6 +1119,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>31</t>
@@ -1052,6 +1128,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>000</t>
@@ -1065,6 +1142,8 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>新疆</t>
     </r>
@@ -1121,6 +1200,10 @@
   </si>
   <si>
     <t>${AMT_a31000_XJ.balance}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：万元</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1131,8 +1214,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="#,##0.000000_ "/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1142,23 +1225,27 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1170,6 +1257,7 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1181,6 +1269,7 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1282,7 +1371,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1368,7 +1457,7 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1392,31 +1481,34 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1430,6 +1522,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1778,7 +1873,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1815,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="7"/>
@@ -1825,19 +1920,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24.95" customHeight="1" thickBot="1">
@@ -1845,586 +1940,586 @@
         <v>5</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="37"/>
       <c r="E4" s="13"/>
-      <c r="F4" s="13" t="s">
-        <v>6</v>
+      <c r="F4" s="40" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.95" customHeight="1">
       <c r="A5" s="32"/>
       <c r="B5" s="42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" s="15" customFormat="1" ht="31.5" customHeight="1">
       <c r="A6" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>10</v>
       </c>
       <c r="C6" s="43"/>
       <c r="D6" s="29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" s="17" customFormat="1" ht="15.95" customHeight="1">
       <c r="A7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="44"/>
       <c r="D7" s="31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" ht="15.95" customHeight="1">
       <c r="A8" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="C8" s="45"/>
+      <c r="D8" s="31" t="s">
         <v>16</v>
-      </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="31" t="s">
-        <v>17</v>
       </c>
       <c r="E8" s="18"/>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" ht="15.95" customHeight="1">
       <c r="A9" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="31" t="s">
         <v>19</v>
-      </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="31" t="s">
-        <v>20</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" ht="15.95" customHeight="1">
       <c r="A10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="31" t="s">
         <v>22</v>
-      </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="31" t="s">
-        <v>23</v>
       </c>
       <c r="E10" s="18"/>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" ht="15.95" customHeight="1">
       <c r="A11" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="31" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="31" t="s">
-        <v>26</v>
       </c>
       <c r="E11" s="18"/>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" ht="15.95" customHeight="1">
       <c r="A12" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="C12" s="45"/>
+      <c r="D12" s="31" t="s">
         <v>28</v>
-      </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="31" t="s">
-        <v>29</v>
       </c>
       <c r="E12" s="18"/>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" ht="15.95" customHeight="1">
       <c r="A13" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="C13" s="45"/>
+      <c r="D13" s="31" t="s">
         <v>31</v>
-      </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="31" t="s">
-        <v>32</v>
       </c>
       <c r="E13" s="18"/>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" ht="15.95" customHeight="1">
       <c r="A14" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="31" t="s">
         <v>34</v>
-      </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="31" t="s">
-        <v>35</v>
       </c>
       <c r="E14" s="18"/>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" ht="15.95" customHeight="1">
       <c r="A15" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="C15" s="45"/>
+      <c r="D15" s="31" t="s">
         <v>37</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="31" t="s">
-        <v>38</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" ht="15.95" customHeight="1">
       <c r="A16" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="C16" s="45"/>
+      <c r="D16" s="31" t="s">
         <v>40</v>
-      </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="31" t="s">
-        <v>41</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" ht="15.95" customHeight="1">
       <c r="A17" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="C17" s="45"/>
+      <c r="D17" s="31" t="s">
         <v>43</v>
-      </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="31" t="s">
-        <v>44</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" ht="15.95" customHeight="1">
       <c r="A18" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="C18" s="45"/>
+      <c r="D18" s="31" t="s">
         <v>46</v>
-      </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="31" t="s">
-        <v>47</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" ht="15.95" customHeight="1">
       <c r="A19" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="C19" s="45"/>
+      <c r="D19" s="31" t="s">
         <v>49</v>
-      </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="31" t="s">
-        <v>50</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" ht="15.95" customHeight="1">
       <c r="A20" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="C20" s="45"/>
+      <c r="D20" s="31" t="s">
         <v>52</v>
-      </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="31" t="s">
-        <v>53</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" ht="15.95" customHeight="1">
       <c r="A21" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="C21" s="45"/>
+      <c r="D21" s="31" t="s">
         <v>55</v>
-      </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="31" t="s">
-        <v>56</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" ht="15.95" customHeight="1">
       <c r="A22" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="C22" s="45"/>
+      <c r="D22" s="31" t="s">
         <v>58</v>
-      </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="31" t="s">
-        <v>59</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" ht="15.95" customHeight="1">
       <c r="A23" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="C23" s="45"/>
+      <c r="D23" s="31" t="s">
         <v>61</v>
-      </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="31" t="s">
-        <v>62</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" ht="15.95" customHeight="1">
       <c r="A24" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="C24" s="45"/>
+      <c r="D24" s="31" t="s">
         <v>64</v>
-      </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="31" t="s">
-        <v>65</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" ht="15.95" customHeight="1">
       <c r="A25" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="C25" s="45"/>
+      <c r="D25" s="31" t="s">
         <v>67</v>
-      </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="31" t="s">
-        <v>68</v>
       </c>
       <c r="E25" s="18"/>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" ht="15.95" customHeight="1">
       <c r="A26" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="40" t="s">
+      <c r="C26" s="45"/>
+      <c r="D26" s="31" t="s">
         <v>70</v>
-      </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="31" t="s">
-        <v>71</v>
       </c>
       <c r="E26" s="18"/>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" ht="15.95" customHeight="1">
       <c r="A27" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="C27" s="45"/>
+      <c r="D27" s="31" t="s">
         <v>73</v>
-      </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="31" t="s">
-        <v>74</v>
       </c>
       <c r="E27" s="18"/>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" ht="15.95" customHeight="1">
       <c r="A28" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="C28" s="45"/>
+      <c r="D28" s="31" t="s">
         <v>76</v>
-      </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="31" t="s">
-        <v>77</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" ht="15.95" customHeight="1">
       <c r="A29" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="40" t="s">
+      <c r="C29" s="45"/>
+      <c r="D29" s="31" t="s">
         <v>79</v>
-      </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="31" t="s">
-        <v>80</v>
       </c>
       <c r="E29" s="18"/>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" ht="15.95" customHeight="1">
       <c r="A30" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="C30" s="45"/>
+      <c r="D30" s="31" t="s">
         <v>82</v>
-      </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="31" t="s">
-        <v>83</v>
       </c>
       <c r="E30" s="18"/>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" ht="15.95" customHeight="1">
       <c r="A31" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="40" t="s">
+      <c r="C31" s="45"/>
+      <c r="D31" s="31" t="s">
         <v>85</v>
-      </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="31" t="s">
-        <v>86</v>
       </c>
       <c r="E31" s="18"/>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" ht="15.95" customHeight="1">
       <c r="A32" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="40" t="s">
+      <c r="C32" s="45"/>
+      <c r="D32" s="31" t="s">
         <v>88</v>
-      </c>
-      <c r="C32" s="40"/>
-      <c r="D32" s="31" t="s">
-        <v>89</v>
       </c>
       <c r="E32" s="18"/>
       <c r="F32"/>
     </row>
     <row r="33" spans="1:6" ht="15.95" customHeight="1">
       <c r="A33" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="C33" s="45"/>
+      <c r="D33" s="31" t="s">
         <v>91</v>
-      </c>
-      <c r="C33" s="40"/>
-      <c r="D33" s="31" t="s">
-        <v>92</v>
       </c>
       <c r="E33" s="18"/>
       <c r="F33"/>
     </row>
     <row r="34" spans="1:6" ht="15.95" customHeight="1">
       <c r="A34" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="C34" s="45"/>
+      <c r="D34" s="31" t="s">
         <v>94</v>
-      </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="31" t="s">
-        <v>95</v>
       </c>
       <c r="E34" s="18"/>
       <c r="F34"/>
     </row>
     <row r="35" spans="1:6" ht="15.95" customHeight="1">
       <c r="A35" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="C35" s="45"/>
+      <c r="D35" s="31" t="s">
         <v>97</v>
-      </c>
-      <c r="C35" s="40"/>
-      <c r="D35" s="31" t="s">
-        <v>98</v>
       </c>
       <c r="E35" s="18"/>
       <c r="F35"/>
     </row>
     <row r="36" spans="1:6" ht="15.95" customHeight="1">
       <c r="A36" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="C36" s="45"/>
+      <c r="D36" s="31" t="s">
         <v>100</v>
-      </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="31" t="s">
-        <v>101</v>
       </c>
       <c r="E36" s="18"/>
       <c r="F36"/>
     </row>
     <row r="37" spans="1:6" ht="15.95" customHeight="1">
       <c r="A37" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="C37" s="45"/>
+      <c r="D37" s="31" t="s">
         <v>103</v>
-      </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="31" t="s">
-        <v>104</v>
       </c>
       <c r="E37" s="18"/>
       <c r="F37"/>
     </row>
     <row r="38" spans="1:6" ht="15.95" customHeight="1">
       <c r="A38" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="C38" s="45"/>
+      <c r="D38" s="31" t="s">
         <v>106</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="31" t="s">
-        <v>107</v>
       </c>
       <c r="E38" s="18"/>
       <c r="F38"/>
     </row>
     <row r="39" spans="1:6" ht="15.95" customHeight="1">
       <c r="A39" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="B39" s="40" t="s">
+      <c r="C39" s="45"/>
+      <c r="D39" s="31" t="s">
         <v>109</v>
-      </c>
-      <c r="C39" s="40"/>
-      <c r="D39" s="31" t="s">
-        <v>110</v>
       </c>
       <c r="E39" s="18"/>
       <c r="F39"/>
     </row>
     <row r="40" spans="1:6" ht="15.95" customHeight="1">
       <c r="A40" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="C40" s="45"/>
+      <c r="D40" s="31" t="s">
         <v>112</v>
-      </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="31" t="s">
-        <v>113</v>
       </c>
       <c r="E40" s="18"/>
       <c r="F40"/>
     </row>
     <row r="41" spans="1:6" ht="15.95" customHeight="1">
       <c r="A41" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="C41" s="45"/>
+      <c r="D41" s="31" t="s">
         <v>115</v>
-      </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="31" t="s">
-        <v>116</v>
       </c>
       <c r="E41" s="18"/>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" ht="15.95" customHeight="1">
       <c r="A42" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="B42" s="40" t="s">
+      <c r="C42" s="45"/>
+      <c r="D42" s="31" t="s">
         <v>118</v>
-      </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="31" t="s">
-        <v>119</v>
       </c>
       <c r="E42" s="18"/>
       <c r="F42"/>
     </row>
     <row r="43" spans="1:6" ht="15.95" customHeight="1" thickBot="1">
       <c r="A43" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" s="46"/>
+      <c r="C43" s="47"/>
       <c r="D43" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E43" s="18"/>
       <c r="F43"/>
     </row>
     <row r="44" spans="1:6" ht="84" customHeight="1">
-      <c r="A44" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="B44" s="47"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
+      <c r="A44" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="B44" s="48"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
     </row>
     <row r="45" spans="1:6" s="24" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A45" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="D45" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="E45" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="F45" s="23" t="s">
         <v>131</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2442,6 +2537,10 @@
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="A44:F44"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
@@ -2452,18 +2551,12 @@
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
@@ -2473,6 +2566,8 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
